--- a/docs/StructureDefinition-LTCProcedureCareActivity.xlsx
+++ b/docs/StructureDefinition-LTCProcedureCareActivity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T05:34:23+08:00</t>
+    <t>2026-02-28T07:16:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCProcedureCareActivity.xlsx
+++ b/docs/StructureDefinition-LTCProcedureCareActivity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T07:16:04+08:00</t>
+    <t>2026-02-28T23:13:53+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCProcedureCareActivity.xlsx
+++ b/docs/StructureDefinition-LTCProcedureCareActivity.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.1</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T23:13:53+08:00</t>
+    <t>2026-03-01T19:25:35+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCProcedureCareActivity.xlsx
+++ b/docs/StructureDefinition-LTCProcedureCareActivity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:25:35+08:00</t>
+    <t>2026-03-02T02:26:08+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCProcedureCareActivity.xlsx
+++ b/docs/StructureDefinition-LTCProcedureCareActivity.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2887" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2882" uniqueCount="529">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T02:26:08+08:00</t>
+    <t>2026-04-02T13:32:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -499,7 +499,7 @@
     <t>Procedure.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(PlanDefinition|ActivityDefinition|Measure|OperationDefinition|Questionnaire)
+    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|ActivityDefinition|4.0.1|Measure|4.0.1|OperationDefinition|4.0.1|Questionnaire|4.0.1)
 </t>
   </si>
   <si>
@@ -636,14 +636,10 @@
     <t>http://hl7.org/fhir/ValueSet/procedure-not-performed-reason</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>CD</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE</t>
+    <t>Event.statusReason</t>
+  </si>
+  <si>
+    <t>.reason.Observation.value</t>
   </si>
   <si>
     <t>Procedure.category</t>
@@ -655,10 +651,13 @@
     <t>對處置/手術進行分類的代碼（例如：「手術處置/手術」）。主要為了搜尋、排序和顯示時使用。</t>
   </si>
   <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
-  </si>
-  <si>
     <t>http://hl7.org/fhir/ValueSet/procedure-category</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
   </si>
   <si>
     <t>Procedure.code</t>
@@ -683,7 +682,19 @@
     <t>A code to identify a specific procedure .</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-code</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-code|4.0.1</t>
+  </si>
+  <si>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>.code</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>OBR-44/OBR-45</t>
   </si>
   <si>
     <t>Procedure.code.id</t>
@@ -750,10 +761,10 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
-    <t>CV</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
   </si>
   <si>
     <t>Procedure.code.coding.id</t>
@@ -947,6 +958,9 @@
   </si>
   <si>
     <t>此為SNOMED CT處置/手術代碼，若機構已有購買相關授權，亦可使用。</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/procedure-code</t>
   </si>
   <si>
     <t>Procedure.code.coding:loinc-procedures</t>
@@ -1283,6 +1297,15 @@
     <t>http://hl7.org/fhir/ValueSet/performer-role</t>
   </si>
   <si>
+    <t>Event.performer.function</t>
+  </si>
+  <si>
+    <t>.functionCode</t>
+  </si>
+  <si>
+    <t>Some combination of STF-18 / PRA-3 / PRT-4 / ROL-3 / ORC-12 / OBR-16 / PV1-7 / PV1-8 / PV1-9 / PV1-17 / OBX-25</t>
+  </si>
+  <si>
     <t>Procedure.performer.actor</t>
   </si>
   <si>
@@ -1388,6 +1411,15 @@
     <t>http://hl7.org/fhir/ValueSet/procedure-reason</t>
   </si>
   <si>
+    <t>Event.reasonCode</t>
+  </si>
+  <si>
+    <t>.reasonCode</t>
+  </si>
+  <si>
+    <t>FiveWs.why[x]</t>
+  </si>
+  <si>
     <t>Procedure.reasonReference</t>
   </si>
   <si>
@@ -1408,12 +1440,6 @@
     <t>Event.reasonReference</t>
   </si>
   <si>
-    <t>.reasonCode</t>
-  </si>
-  <si>
-    <t>FiveWs.why[x]</t>
-  </si>
-  <si>
     <t>Procedure.bodySite</t>
   </si>
   <si>
@@ -1429,6 +1455,12 @@
     <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
+    <t>.targetSiteCode</t>
+  </si>
+  <si>
+    <t>OBX-20</t>
+  </si>
+  <si>
     <t>Procedure.outcome</t>
   </si>
   <si>
@@ -1442,6 +1474,9 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/procedure-outcome</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=OUT].target.text</t>
   </si>
   <si>
     <t>Procedure.report</t>
@@ -1478,6 +1513,9 @@
     <t>http://hl7.org/fhir/ValueSet/condition-code</t>
   </si>
   <si>
+    <t>.outboundRelationship[typeCode=OUTC].target[classCode=OBS, code="complication", moodCode=EVN].value</t>
+  </si>
+  <si>
     <t>Procedure.complicationDetail</t>
   </si>
   <si>
@@ -1494,9 +1532,6 @@
     <t>這是用來記錄作為處置/手術結果的病情、問題或診斷，而不是作為處置/手術原因的病情、問題或診斷。</t>
   </si>
   <si>
-    <t>.outboundRelationship[typeCode=OUTC].target[classCode=OBS, code="complication", moodCode=EVN].value</t>
-  </si>
-  <si>
     <t>Procedure.followUp</t>
   </si>
   <si>
@@ -1507,6 +1542,9 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/procedure-followup</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=COMP].target[classCode=ACT, moodCode=INT].code</t>
   </si>
   <si>
     <t>Procedure.note</t>
@@ -1567,10 +1605,13 @@
     <t>http://hl7.org/fhir/ValueSet/device-action</t>
   </si>
   <si>
+    <t>.inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="procedure device action"].value=:procedure device action codes</t>
+  </si>
+  <si>
     <t>Procedure.focalDevice.manipulated</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device)
+    <t xml:space="preserve">Reference(Device|4.0.1)
 </t>
   </si>
   <si>
@@ -1616,6 +1657,9 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/device-kind</t>
+  </si>
+  <si>
+    <t>participation[typeCode=Dev].role[classCode=MANU]</t>
   </si>
 </sst>
 </file>
@@ -1971,9 +2015,9 @@
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="95.5546875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="122.22265625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="65.0703125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="90.15625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3827,7 +3871,7 @@
         <v>20</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K17" t="s" s="2">
         <v>191</v>
@@ -3898,13 +3942,13 @@
         <v>86</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>199</v>
@@ -3913,15 +3957,15 @@
         <v>20</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>200</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3941,20 +3985,18 @@
         <v>20</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K18" t="s" s="2">
         <v>191</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="M18" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>204</v>
-      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>20</v>
@@ -3985,7 +4027,7 @@
         <v>196</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>20</v>
@@ -4003,7 +4045,7 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -4012,7 +4054,7 @@
         <v>86</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>98</v>
@@ -4021,13 +4063,13 @@
         <v>20</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>20</v>
+        <v>205</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>200</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
@@ -4055,7 +4097,7 @@
         <v>20</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K19" t="s" s="2">
         <v>191</v>
@@ -4066,9 +4108,7 @@
       <c r="M19" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="N19" t="s" s="2">
-        <v>204</v>
-      </c>
+      <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
         <v>210</v>
       </c>
@@ -4128,30 +4168,30 @@
         <v>86</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>20</v>
+        <v>214</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>20</v>
+        <v>216</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4174,13 +4214,13 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4231,7 +4271,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -4249,7 +4289,7 @@
         <v>20</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>20</v>
@@ -4260,10 +4300,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4289,10 +4329,10 @@
         <v>133</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4331,19 +4371,19 @@
         <v>20</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -4372,10 +4412,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4395,22 +4435,22 @@
         <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -4447,17 +4487,17 @@
         <v>20</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="AC22" s="2"/>
       <c r="AD22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -4466,7 +4506,7 @@
         <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>98</v>
@@ -4475,21 +4515,21 @@
         <v>20</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4512,13 +4552,13 @@
         <v>20</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4569,7 +4609,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -4587,7 +4627,7 @@
         <v>20</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>20</v>
@@ -4598,10 +4638,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4627,13 +4667,13 @@
         <v>133</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4671,19 +4711,19 @@
         <v>20</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4712,10 +4752,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4741,16 +4781,16 @@
         <v>100</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -4760,7 +4800,7 @@
         <v>20</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>20</v>
@@ -4799,7 +4839,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4817,21 +4857,21 @@
         <v>20</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4854,16 +4894,16 @@
         <v>87</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4913,7 +4953,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4931,21 +4971,21 @@
         <v>20</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4971,14 +5011,14 @@
         <v>106</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -5027,7 +5067,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -5045,21 +5085,21 @@
         <v>20</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5082,17 +5122,17 @@
         <v>87</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -5141,7 +5181,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -5159,21 +5199,21 @@
         <v>20</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5196,19 +5236,19 @@
         <v>87</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -5257,7 +5297,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -5275,24 +5315,24 @@
         <v>20</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>20</v>
@@ -5311,22 +5351,22 @@
         <v>20</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>20</v>
@@ -5354,10 +5394,10 @@
         <v>184</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>20</v>
@@ -5375,7 +5415,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -5384,7 +5424,7 @@
         <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>98</v>
@@ -5393,24 +5433,24 @@
         <v>20</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>20</v>
@@ -5429,22 +5469,22 @@
         <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -5472,10 +5512,10 @@
         <v>184</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>20</v>
@@ -5493,7 +5533,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5502,7 +5542,7 @@
         <v>78</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>98</v>
@@ -5511,24 +5551,24 @@
         <v>20</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>20</v>
@@ -5547,22 +5587,22 @@
         <v>20</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5590,10 +5630,10 @@
         <v>184</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>20</v>
@@ -5611,7 +5651,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5620,7 +5660,7 @@
         <v>78</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>98</v>
@@ -5629,24 +5669,24 @@
         <v>20</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>20</v>
@@ -5665,22 +5705,22 @@
         <v>20</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -5708,10 +5748,10 @@
         <v>184</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>20</v>
@@ -5729,7 +5769,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5738,7 +5778,7 @@
         <v>78</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>98</v>
@@ -5747,24 +5787,24 @@
         <v>20</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>20</v>
@@ -5783,22 +5823,22 @@
         <v>20</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -5826,10 +5866,10 @@
         <v>184</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>213</v>
+        <v>304</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>20</v>
@@ -5847,7 +5887,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5856,7 +5896,7 @@
         <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>98</v>
@@ -5865,24 +5905,24 @@
         <v>20</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>20</v>
@@ -5901,22 +5941,22 @@
         <v>20</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -5945,7 +5985,7 @@
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>20</v>
@@ -5963,7 +6003,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5972,7 +6012,7 @@
         <v>78</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>98</v>
@@ -5981,21 +6021,21 @@
         <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6018,19 +6058,19 @@
         <v>87</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -6079,7 +6119,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -6097,25 +6137,25 @@
         <v>20</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6134,13 +6174,13 @@
         <v>87</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6191,7 +6231,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>86</v>
@@ -6206,24 +6246,24 @@
         <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6246,13 +6286,13 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6303,7 +6343,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -6321,7 +6361,7 @@
         <v>20</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>20</v>
@@ -6332,10 +6372,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6364,7 +6404,7 @@
         <v>134</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="N39" t="s" s="2">
         <v>136</v>
@@ -6405,19 +6445,19 @@
         <v>20</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -6435,7 +6475,7 @@
         <v>20</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>20</v>
@@ -6446,10 +6486,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6472,16 +6512,16 @@
         <v>87</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6531,7 +6571,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -6540,7 +6580,7 @@
         <v>86</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>98</v>
@@ -6560,10 +6600,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6589,13 +6629,13 @@
         <v>100</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6624,10 +6664,10 @@
         <v>195</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>20</v>
@@ -6645,7 +6685,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6674,10 +6714,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6703,13 +6743,13 @@
         <v>145</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6759,7 +6799,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6777,7 +6817,7 @@
         <v>20</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>20</v>
@@ -6788,10 +6828,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6814,16 +6854,16 @@
         <v>87</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6873,7 +6913,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6902,10 +6942,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6928,16 +6968,16 @@
         <v>87</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6987,7 +7027,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -7002,24 +7042,24 @@
         <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7042,16 +7082,16 @@
         <v>87</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7089,17 +7129,17 @@
         <v>20</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="AC45" s="2"/>
       <c r="AD45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -7114,27 +7154,27 @@
         <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>20</v>
@@ -7156,16 +7196,16 @@
         <v>87</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7215,7 +7255,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -7230,24 +7270,24 @@
         <v>98</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7270,13 +7310,13 @@
         <v>87</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7327,7 +7367,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -7345,10 +7385,10 @@
         <v>20</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>20</v>
@@ -7356,10 +7396,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7382,13 +7422,13 @@
         <v>87</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7439,7 +7479,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7457,10 +7497,10 @@
         <v>20</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>20</v>
@@ -7468,10 +7508,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7494,13 +7534,13 @@
         <v>87</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7551,7 +7591,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7566,10 +7606,10 @@
         <v>98</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>20</v>
@@ -7580,10 +7620,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7606,13 +7646,13 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7663,7 +7703,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7681,7 +7721,7 @@
         <v>20</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>20</v>
@@ -7692,10 +7732,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7724,7 +7764,7 @@
         <v>134</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>136</v>
@@ -7777,7 +7817,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7795,7 +7835,7 @@
         <v>20</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>20</v>
@@ -7806,14 +7846,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7835,10 +7875,10 @@
         <v>133</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>136</v>
@@ -7893,7 +7933,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7922,10 +7962,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7945,22 +7985,20 @@
         <v>20</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K53" t="s" s="2">
         <v>191</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>204</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -7991,7 +8029,7 @@
         <v>196</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>20</v>
@@ -8009,7 +8047,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -8018,30 +8056,30 @@
         <v>86</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>20</v>
+        <v>411</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>199</v>
+        <v>412</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>200</v>
+        <v>413</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8064,17 +8102,17 @@
         <v>87</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
@@ -8123,7 +8161,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>86</v>
@@ -8138,24 +8176,24 @@
         <v>98</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>414</v>
+        <v>422</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8178,13 +8216,13 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8235,7 +8273,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -8253,7 +8291,7 @@
         <v>20</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>20</v>
@@ -8264,10 +8302,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8296,7 +8334,7 @@
         <v>134</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>136</v>
@@ -8337,19 +8375,19 @@
         <v>20</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -8367,7 +8405,7 @@
         <v>20</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>20</v>
@@ -8378,10 +8416,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8404,16 +8442,16 @@
         <v>87</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8463,7 +8501,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -8472,7 +8510,7 @@
         <v>86</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>98</v>
@@ -8492,10 +8530,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8521,13 +8559,13 @@
         <v>100</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8556,10 +8594,10 @@
         <v>195</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>20</v>
@@ -8577,7 +8615,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8606,10 +8644,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8635,13 +8673,13 @@
         <v>145</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8691,7 +8729,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8709,7 +8747,7 @@
         <v>20</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>20</v>
@@ -8720,10 +8758,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8746,16 +8784,16 @@
         <v>87</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8805,7 +8843,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
@@ -8834,10 +8872,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8860,17 +8898,17 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>20</v>
@@ -8919,7 +8957,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
@@ -8937,7 +8975,7 @@
         <v>20</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>20</v>
@@ -8948,10 +8986,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8974,17 +9012,17 @@
         <v>87</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>20</v>
@@ -9033,7 +9071,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
@@ -9051,10 +9089,10 @@
         <v>20</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>20</v>
@@ -9062,10 +9100,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9085,19 +9123,19 @@
         <v>20</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K63" t="s" s="2">
         <v>191</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9129,7 +9167,7 @@
         <v>196</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>20</v>
@@ -9147,7 +9185,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
@@ -9156,30 +9194,30 @@
         <v>78</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>20</v>
+        <v>448</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>199</v>
+        <v>449</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>20</v>
+        <v>450</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>200</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9202,16 +9240,16 @@
         <v>87</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9261,7 +9299,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
@@ -9276,13 +9314,13 @@
         <v>98</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>20</v>
@@ -9290,10 +9328,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9313,19 +9351,19 @@
         <v>20</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K65" t="s" s="2">
         <v>191</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9357,7 +9395,7 @@
         <v>196</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>20</v>
@@ -9375,7 +9413,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
@@ -9384,7 +9422,7 @@
         <v>78</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>98</v>
@@ -9393,21 +9431,21 @@
         <v>20</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>199</v>
+        <v>462</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>200</v>
+        <v>463</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9427,19 +9465,19 @@
         <v>20</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K66" t="s" s="2">
         <v>191</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9471,7 +9509,7 @@
         <v>196</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>20</v>
@@ -9489,7 +9527,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -9498,7 +9536,7 @@
         <v>86</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>98</v>
@@ -9507,21 +9545,21 @@
         <v>20</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>199</v>
+        <v>469</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>200</v>
+        <v>20</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9544,16 +9582,16 @@
         <v>20</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9603,7 +9641,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -9621,7 +9659,7 @@
         <v>20</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>20</v>
@@ -9632,10 +9670,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9661,13 +9699,13 @@
         <v>191</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9699,7 +9737,7 @@
         <v>196</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>20</v>
@@ -9717,7 +9755,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
@@ -9726,7 +9764,7 @@
         <v>78</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>98</v>
@@ -9735,21 +9773,21 @@
         <v>20</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>199</v>
+        <v>481</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>200</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>469</v>
+        <v>482</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>469</v>
+        <v>482</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9772,17 +9810,17 @@
         <v>20</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>472</v>
+        <v>485</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>473</v>
+        <v>486</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>20</v>
@@ -9831,7 +9869,7 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>469</v>
+        <v>482</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
@@ -9849,7 +9887,7 @@
         <v>20</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>20</v>
@@ -9860,10 +9898,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9889,14 +9927,12 @@
         <v>191</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>204</v>
-      </c>
+        <v>489</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>20</v>
@@ -9927,7 +9963,7 @@
         <v>196</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>20</v>
@@ -9945,7 +9981,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -9954,7 +9990,7 @@
         <v>78</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>98</v>
@@ -9963,21 +9999,21 @@
         <v>20</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>199</v>
+        <v>491</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>200</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>479</v>
+        <v>492</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>479</v>
+        <v>492</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10000,13 +10036,13 @@
         <v>20</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>480</v>
+        <v>493</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>481</v>
+        <v>494</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>482</v>
+        <v>495</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10057,7 +10093,7 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>479</v>
+        <v>492</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
@@ -10072,24 +10108,24 @@
         <v>98</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>483</v>
+        <v>496</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>484</v>
+        <v>497</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>485</v>
+        <v>498</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>486</v>
+        <v>499</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>486</v>
+        <v>499</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10112,13 +10148,13 @@
         <v>20</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>487</v>
+        <v>500</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10169,7 +10205,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>486</v>
+        <v>499</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
@@ -10187,7 +10223,7 @@
         <v>20</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>489</v>
+        <v>502</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>20</v>
@@ -10198,10 +10234,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>490</v>
+        <v>503</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>490</v>
+        <v>503</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10224,13 +10260,13 @@
         <v>20</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10281,7 +10317,7 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>77</v>
@@ -10299,7 +10335,7 @@
         <v>20</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>20</v>
@@ -10310,10 +10346,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>491</v>
+        <v>504</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>491</v>
+        <v>504</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10342,7 +10378,7 @@
         <v>134</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>136</v>
@@ -10395,7 +10431,7 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>77</v>
@@ -10413,7 +10449,7 @@
         <v>20</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>20</v>
@@ -10424,14 +10460,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>492</v>
+        <v>505</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>492</v>
+        <v>505</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10453,10 +10489,10 @@
         <v>133</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>136</v>
@@ -10511,7 +10547,7 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>77</v>
@@ -10540,10 +10576,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>493</v>
+        <v>506</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>493</v>
+        <v>506</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10569,14 +10605,12 @@
         <v>191</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>494</v>
+        <v>507</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>204</v>
-      </c>
+        <v>508</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>20</v>
@@ -10604,10 +10638,10 @@
         <v>111</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>497</v>
+        <v>510</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>20</v>
@@ -10625,7 +10659,7 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>493</v>
+        <v>506</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>77</v>
@@ -10634,7 +10668,7 @@
         <v>86</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>98</v>
@@ -10643,21 +10677,21 @@
         <v>20</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>199</v>
+        <v>511</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>200</v>
+        <v>20</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>498</v>
+        <v>512</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>498</v>
+        <v>512</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10680,13 +10714,13 @@
         <v>20</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>499</v>
+        <v>513</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>501</v>
+        <v>515</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10737,7 +10771,7 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>498</v>
+        <v>512</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>86</v>
@@ -10755,7 +10789,7 @@
         <v>20</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>502</v>
+        <v>516</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>20</v>
@@ -10766,10 +10800,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>503</v>
+        <v>517</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>503</v>
+        <v>517</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10792,19 +10826,19 @@
         <v>20</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>504</v>
+        <v>518</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>507</v>
+        <v>521</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>20</v>
@@ -10853,7 +10887,7 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>503</v>
+        <v>517</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>77</v>
@@ -10871,7 +10905,7 @@
         <v>20</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>20</v>
@@ -10882,10 +10916,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>510</v>
+        <v>524</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>510</v>
+        <v>524</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10911,13 +10945,13 @@
         <v>191</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>511</v>
+        <v>525</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>512</v>
+        <v>526</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>507</v>
+        <v>521</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10949,7 +10983,7 @@
         <v>196</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>513</v>
+        <v>527</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>20</v>
@@ -10967,7 +11001,7 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>510</v>
+        <v>524</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>77</v>
@@ -10976,7 +11010,7 @@
         <v>78</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>98</v>
@@ -10985,13 +11019,13 @@
         <v>20</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>199</v>
+        <v>528</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>200</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/docs/StructureDefinition-LTCProcedureCareActivity.xlsx
+++ b/docs/StructureDefinition-LTCProcedureCareActivity.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$80</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2882" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2919" uniqueCount="540">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T13:32:15+08:00</t>
+    <t>2026-04-03T21:17:06+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -767,12 +767,114 @@
     <t>C*E.1-8, C*E.10-22</t>
   </si>
   <si>
+    <t>Procedure.code.coding:icd10-pcs-2023</t>
+  </si>
+  <si>
+    <t>icd10-pcs-2023</t>
+  </si>
+  <si>
+    <t>此為臺灣衛生福利部中央健康保險署（NHI）維護之2023年中文版ICD-10-PCS代碼，涵蓋範圍相對完整，可免費使用，可優先選用此代碼。</t>
+  </si>
+  <si>
+    <t>處置/手術的識別；應填入所綁定值集中的其中一個代碼。</t>
+  </si>
+  <si>
+    <t>https://twcore.mohw.gov.tw/ig/twcore/ValueSet/icd-10-pcs-2023-tw</t>
+  </si>
+  <si>
+    <t>Procedure.code.coding:icd10-pcs-2021</t>
+  </si>
+  <si>
+    <t>icd10-pcs-2021</t>
+  </si>
+  <si>
+    <t>此為臺灣衛生福利部中央健康保險署（NHI）維護之2021年中文版ICD-10-PCS代碼，涵蓋範圍相對完整，可免費使用，可優先選用此代碼。</t>
+  </si>
+  <si>
+    <t>https://twcore.mohw.gov.tw/ig/twcore/ValueSet/icd-10-pcs-2021-tw</t>
+  </si>
+  <si>
+    <t>Procedure.code.coding:icd10-pcs-2014</t>
+  </si>
+  <si>
+    <t>icd10-pcs-2014</t>
+  </si>
+  <si>
+    <t>此為臺灣衛生福利部中央健康保險署（NHI）維護之2014年中文版ICD-10-PCS代碼，涵蓋範圍相對完整，可免費使用，可優先選用此代碼。</t>
+  </si>
+  <si>
+    <t>https://twcore.mohw.gov.tw/ig/twcore/ValueSet/icd-10-pcs-2014-tw</t>
+  </si>
+  <si>
+    <t>Procedure.code.coding:medical-service-payment</t>
+  </si>
+  <si>
+    <t>medical-service-payment</t>
+  </si>
+  <si>
+    <t>此為臺灣衛生福利部中央健康保險署（NHI）維護之醫療服務給付項目，主要針對申報使用，可免費使用，可依情境選用此代碼。</t>
+  </si>
+  <si>
+    <t>https://twcore.mohw.gov.tw/ig/twcore/ValueSet/procedure-tw</t>
+  </si>
+  <si>
+    <t>Procedure.code.coding:sct-procedures</t>
+  </si>
+  <si>
+    <t>sct-procedures</t>
+  </si>
+  <si>
+    <t>此為SNOMED CT處置/手術代碼，若機構已有購買相關授權，亦可使用。</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/procedure-code</t>
+  </si>
+  <si>
+    <t>Procedure.code.coding:loinc-procedures</t>
+  </si>
+  <si>
+    <t>loinc-procedures</t>
+  </si>
+  <si>
+    <t>由專門術語系統（terminology system）定義的代碼</t>
+  </si>
+  <si>
+    <t>由專門術語系統（terminology system）所定義之代碼的參照</t>
+  </si>
+  <si>
+    <t>代碼可以在列舉清單（enumerations）或代碼清單（code lists）中非常隨意地定義，直至有非常正式的定義，例如：SNOMED CT—更多資訊見HL7 v3核心原則（Core Principles ）。編碼的排序是未定義的因而 **必須沒有（SHALL NOT）** 被用來推斷意義。一般來說，最多只有一個編碼值（coding values）會被標記為UserSelected = true。</t>
+  </si>
+  <si>
+    <t>允許代碼系統中的替代編碼，以及翻譯到其他編碼系統。</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+  </si>
+  <si>
+    <t>Procedure.code.coding:ltcServiceItem</t>
+  </si>
+  <si>
+    <t>ltcServiceItem</t>
+  </si>
+  <si>
+    <t>臺灣長照服務項目代碼（AA..GA 系列）</t>
+  </si>
+  <si>
+    <t>http://ltc-ig.fhir.tw/ValueSet/vs-tw-ltc-service-item</t>
+  </si>
+  <si>
+    <t>Procedure.code.coding:ltcServiceItem.id</t>
+  </si>
+  <si>
     <t>Procedure.code.coding.id</t>
   </si>
   <si>
     <t>resource中資料項目的唯一ID（用於內部參照），這可以是任何不含空格的字串。</t>
   </si>
   <si>
+    <t>Procedure.code.coding:ltcServiceItem.extension</t>
+  </si>
+  <si>
     <t>Procedure.code.coding.extension</t>
   </si>
   <si>
@@ -782,6 +884,9 @@
     <t>無論使用或定義擴充的機構或管轄區，任何應用程式、專案或標準使用擴充都不背負任何污名（stigma）。使用擴充是允許FHIR規範為每個人保留一個核心的簡易性。</t>
   </si>
   <si>
+    <t>Procedure.code.coding:ltcServiceItem.system</t>
+  </si>
+  <si>
     <t>Procedure.code.coding.system</t>
   </si>
   <si>
@@ -797,7 +902,7 @@
     <t>需要明確說明符號定義的來源</t>
   </si>
   <si>
-    <t>http://snomed.info/sct</t>
+    <t>http://ltc-ig.fhir.tw/CodeSystem/cs-tw-ltc-service-item</t>
   </si>
   <si>
     <t>Coding.system</t>
@@ -809,6 +914,9 @@
     <t>C*E.3</t>
   </si>
   <si>
+    <t>Procedure.code.coding:ltcServiceItem.version</t>
+  </si>
+  <si>
     <t>Procedure.code.coding.version</t>
   </si>
   <si>
@@ -830,6 +938,9 @@
     <t>C*E.7</t>
   </si>
   <si>
+    <t>Procedure.code.coding:ltcServiceItem.code</t>
+  </si>
+  <si>
     <t>Procedure.code.coding.code</t>
   </si>
   <si>
@@ -851,6 +962,9 @@
     <t>C*E.1</t>
   </si>
   <si>
+    <t>Procedure.code.coding:ltcServiceItem.display</t>
+  </si>
+  <si>
     <t>Procedure.code.coding.display</t>
   </si>
   <si>
@@ -870,6 +984,9 @@
   </si>
   <si>
     <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>Procedure.code.coding:ltcServiceItem.userSelected</t>
   </si>
   <si>
     <t>Procedure.code.coding.userSelected</t>
@@ -898,90 +1015,6 @@
   </si>
   <si>
     <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>Procedure.code.coding:icd10-pcs-2023</t>
-  </si>
-  <si>
-    <t>icd10-pcs-2023</t>
-  </si>
-  <si>
-    <t>此為臺灣衛生福利部中央健康保險署（NHI）維護之2023年中文版ICD-10-PCS代碼，涵蓋範圍相對完整，可免費使用，可優先選用此代碼。</t>
-  </si>
-  <si>
-    <t>處置/手術的識別；應填入所綁定值集中的其中一個代碼。</t>
-  </si>
-  <si>
-    <t>https://twcore.mohw.gov.tw/ig/twcore/ValueSet/icd-10-pcs-2023-tw</t>
-  </si>
-  <si>
-    <t>Procedure.code.coding:icd10-pcs-2021</t>
-  </si>
-  <si>
-    <t>icd10-pcs-2021</t>
-  </si>
-  <si>
-    <t>此為臺灣衛生福利部中央健康保險署（NHI）維護之2021年中文版ICD-10-PCS代碼，涵蓋範圍相對完整，可免費使用，可優先選用此代碼。</t>
-  </si>
-  <si>
-    <t>https://twcore.mohw.gov.tw/ig/twcore/ValueSet/icd-10-pcs-2021-tw</t>
-  </si>
-  <si>
-    <t>Procedure.code.coding:icd10-pcs-2014</t>
-  </si>
-  <si>
-    <t>icd10-pcs-2014</t>
-  </si>
-  <si>
-    <t>此為臺灣衛生福利部中央健康保險署（NHI）維護之2014年中文版ICD-10-PCS代碼，涵蓋範圍相對完整，可免費使用，可優先選用此代碼。</t>
-  </si>
-  <si>
-    <t>https://twcore.mohw.gov.tw/ig/twcore/ValueSet/icd-10-pcs-2014-tw</t>
-  </si>
-  <si>
-    <t>Procedure.code.coding:medical-service-payment</t>
-  </si>
-  <si>
-    <t>medical-service-payment</t>
-  </si>
-  <si>
-    <t>此為臺灣衛生福利部中央健康保險署（NHI）維護之醫療服務給付項目，主要針對申報使用，可免費使用，可依情境選用此代碼。</t>
-  </si>
-  <si>
-    <t>https://twcore.mohw.gov.tw/ig/twcore/ValueSet/procedure-tw</t>
-  </si>
-  <si>
-    <t>Procedure.code.coding:sct-procedures</t>
-  </si>
-  <si>
-    <t>sct-procedures</t>
-  </si>
-  <si>
-    <t>此為SNOMED CT處置/手術代碼，若機構已有購買相關授權，亦可使用。</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-code</t>
-  </si>
-  <si>
-    <t>Procedure.code.coding:loinc-procedures</t>
-  </si>
-  <si>
-    <t>loinc-procedures</t>
-  </si>
-  <si>
-    <t>由專門術語系統（terminology system）定義的代碼</t>
-  </si>
-  <si>
-    <t>由專門術語系統（terminology system）所定義之代碼的參照</t>
-  </si>
-  <si>
-    <t>代碼可以在列舉清單（enumerations）或代碼清單（code lists）中非常隨意地定義，直至有非常正式的定義，例如：SNOMED CT—更多資訊見HL7 v3核心原則（Core Principles ）。編碼的排序是未定義的因而 **必須沒有（SHALL NOT）** 被用來推斷意義。一般來說，最多只有一個編碼值（coding values）會被標記為UserSelected = true。</t>
-  </si>
-  <si>
-    <t>允許代碼系統中的替代編碼，以及翻譯到其他編碼系統。</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
     <t>Procedure.code.text</t>
@@ -1976,10 +2009,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN79"/>
+  <dimension ref="A1:AN80"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="39.42578125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="41.5078125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="33.2890625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="20.859375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
@@ -4524,14 +4557,16 @@
         <v>239</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>240</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="D23" t="s" s="2">
         <v>20</v>
       </c>
@@ -4543,25 +4578,29 @@
         <v>86</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
       </c>
@@ -4585,13 +4624,13 @@
         <v>20</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>20</v>
+        <v>184</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>20</v>
+        <v>243</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>20</v>
+        <v>244</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>20</v>
@@ -4609,41 +4648,43 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>20</v>
+        <v>239</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="D24" t="s" s="2">
         <v>20</v>
       </c>
@@ -4652,30 +4693,32 @@
         <v>77</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>133</v>
+        <v>231</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>225</v>
+        <v>247</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
       </c>
@@ -4699,31 +4742,31 @@
         <v>20</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>20</v>
+        <v>184</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>20</v>
+        <v>243</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>20</v>
+        <v>248</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>226</v>
+        <v>20</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>227</v>
+        <v>20</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>228</v>
+        <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4735,35 +4778,37 @@
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>138</v>
+        <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>20</v>
+        <v>238</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>20</v>
+        <v>239</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="C25" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="D25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>86</v>
@@ -4778,19 +4823,19 @@
         <v>87</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>100</v>
+        <v>231</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -4800,7 +4845,7 @@
         <v>20</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>250</v>
+        <v>20</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>20</v>
@@ -4815,13 +4860,13 @@
         <v>20</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>20</v>
+        <v>184</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>20</v>
+        <v>243</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>20</v>
+        <v>252</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>20</v>
@@ -4839,13 +4884,13 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
@@ -4857,23 +4902,25 @@
         <v>20</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN25" t="s" s="2">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
         <v>253</v>
       </c>
-    </row>
-    <row r="26" hidden="true">
-      <c r="A26" t="s" s="2">
+      <c r="B26" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="C26" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="B26" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>20</v>
       </c>
@@ -4885,7 +4932,7 @@
         <v>86</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>20</v>
@@ -4894,18 +4941,20 @@
         <v>87</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="L26" t="s" s="2">
         <v>255</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>256</v>
+        <v>233</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
       </c>
@@ -4929,13 +4978,13 @@
         <v>20</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>20</v>
+        <v>184</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>20</v>
+        <v>243</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>20</v>
+        <v>256</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>20</v>
@@ -4953,13 +5002,13 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>258</v>
+        <v>237</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
@@ -4971,29 +5020,31 @@
         <v>20</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>259</v>
+        <v>238</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>260</v>
+        <v>239</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="C27" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="D27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>86</v>
@@ -5008,17 +5059,19 @@
         <v>87</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>106</v>
+        <v>231</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="O27" t="s" s="2">
-        <v>264</v>
+        <v>235</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -5043,13 +5096,13 @@
         <v>20</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>20</v>
+        <v>184</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>20</v>
+        <v>243</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>20</v>
+        <v>260</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>20</v>
@@ -5067,13 +5120,13 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>265</v>
+        <v>237</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
@@ -5085,29 +5138,31 @@
         <v>20</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>266</v>
+        <v>238</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>262</v>
+      </c>
       <c r="D28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>86</v>
@@ -5122,17 +5177,19 @@
         <v>87</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="O28" t="s" s="2">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -5157,13 +5214,11 @@
         <v>20</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>20</v>
+        <v>267</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>20</v>
@@ -5181,13 +5236,13 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>272</v>
+        <v>237</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
@@ -5199,23 +5254,25 @@
         <v>20</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>273</v>
+        <v>238</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>274</v>
+        <v>239</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="C29" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>269</v>
+      </c>
       <c r="D29" t="s" s="2">
         <v>20</v>
       </c>
@@ -5227,7 +5284,7 @@
         <v>86</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>20</v>
@@ -5236,19 +5293,19 @@
         <v>87</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>276</v>
+        <v>231</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>278</v>
+        <v>233</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>279</v>
+        <v>234</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>280</v>
+        <v>235</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -5273,13 +5330,11 @@
         <v>20</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>20</v>
+        <v>271</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>20</v>
@@ -5297,13 +5352,13 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>281</v>
+        <v>237</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
@@ -5315,25 +5370,23 @@
         <v>20</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>282</v>
+        <v>238</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>283</v>
+        <v>239</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="C30" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
         <v>20</v>
       </c>
@@ -5345,29 +5398,25 @@
         <v>86</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>286</v>
+        <v>220</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>235</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>20</v>
       </c>
@@ -5391,13 +5440,13 @@
         <v>20</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>184</v>
+        <v>20</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>287</v>
+        <v>20</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>288</v>
+        <v>20</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>20</v>
@@ -5415,43 +5464,41 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>239</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="C31" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>20</v>
       </c>
@@ -5460,32 +5507,30 @@
         <v>77</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>231</v>
+        <v>133</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>291</v>
+        <v>225</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>233</v>
+        <v>277</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>235</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>20</v>
       </c>
@@ -5509,31 +5554,31 @@
         <v>20</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>184</v>
+        <v>20</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>287</v>
+        <v>20</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>292</v>
+        <v>20</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>20</v>
+        <v>226</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>20</v>
+        <v>227</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>20</v>
+        <v>228</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5545,37 +5590,35 @@
         <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>238</v>
+        <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>239</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="C32" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>86</v>
@@ -5590,19 +5633,19 @@
         <v>87</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>231</v>
+        <v>100</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>233</v>
+        <v>282</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>234</v>
+        <v>283</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>235</v>
+        <v>284</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5612,7 +5655,7 @@
         <v>20</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>20</v>
+        <v>285</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>20</v>
@@ -5627,13 +5670,13 @@
         <v>20</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>184</v>
+        <v>20</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>287</v>
+        <v>20</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>296</v>
+        <v>20</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>20</v>
@@ -5651,13 +5694,13 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>237</v>
+        <v>286</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>20</v>
@@ -5669,25 +5712,23 @@
         <v>20</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>238</v>
+        <v>287</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>239</v>
+        <v>288</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>298</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>20</v>
       </c>
@@ -5699,7 +5740,7 @@
         <v>86</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>20</v>
@@ -5708,20 +5749,18 @@
         <v>87</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>233</v>
+        <v>292</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>235</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>20</v>
       </c>
@@ -5745,13 +5784,13 @@
         <v>20</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>184</v>
+        <v>20</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>287</v>
+        <v>20</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>20</v>
@@ -5769,13 +5808,13 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>237</v>
+        <v>294</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
@@ -5787,31 +5826,29 @@
         <v>20</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>238</v>
+        <v>295</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>239</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>86</v>
@@ -5826,19 +5863,17 @@
         <v>87</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>231</v>
+        <v>106</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>235</v>
+        <v>301</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -5863,13 +5898,13 @@
         <v>20</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>184</v>
+        <v>20</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>287</v>
+        <v>20</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>304</v>
+        <v>20</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>20</v>
@@ -5887,13 +5922,13 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>237</v>
+        <v>302</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
@@ -5905,13 +5940,13 @@
         <v>20</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>238</v>
+        <v>303</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>239</v>
+        <v>304</v>
       </c>
     </row>
     <row r="35">
@@ -5919,11 +5954,9 @@
         <v>305</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="C35" t="s" s="2">
         <v>306</v>
       </c>
+      <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>20</v>
       </c>
@@ -5944,7 +5977,7 @@
         <v>87</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="L35" t="s" s="2">
         <v>307</v>
@@ -5952,11 +5985,9 @@
       <c r="M35" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="N35" s="2"/>
+      <c r="O35" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -5981,11 +6012,13 @@
         <v>20</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="Y35" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z35" t="s" s="2">
-        <v>311</v>
+        <v>20</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>20</v>
@@ -6003,13 +6036,13 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>237</v>
+        <v>310</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
@@ -6021,21 +6054,21 @@
         <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>238</v>
+        <v>311</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>239</v>
+        <v>312</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6049,7 +6082,7 @@
         <v>86</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>20</v>
@@ -6058,19 +6091,19 @@
         <v>87</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>219</v>
+        <v>315</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -6119,7 +6152,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -6137,29 +6170,29 @@
         <v>20</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>321</v>
+        <v>20</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>86</v>
@@ -6174,16 +6207,20 @@
         <v>87</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>322</v>
+        <v>219</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+        <v>325</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
       </c>
@@ -6231,10 +6268,10 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>86</v>
@@ -6246,53 +6283,53 @@
         <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>325</v>
+        <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>327</v>
+        <v>20</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>20</v>
+        <v>332</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>86</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>219</v>
+        <v>333</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6343,10 +6380,10 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>222</v>
+        <v>331</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>86</v>
@@ -6355,38 +6392,38 @@
         <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>20</v>
+        <v>336</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>223</v>
+        <v>337</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>20</v>
+        <v>338</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>20</v>
+        <v>339</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>132</v>
+        <v>20</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -6398,17 +6435,15 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>133</v>
+        <v>219</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>134</v>
+        <v>341</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -6445,31 +6480,31 @@
         <v>20</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>226</v>
+        <v>20</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>227</v>
+        <v>20</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>228</v>
+        <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>138</v>
+        <v>20</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>20</v>
@@ -6484,44 +6519,44 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>20</v>
+        <v>132</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>219</v>
+        <v>133</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>335</v>
+        <v>134</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>337</v>
+        <v>136</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6559,37 +6594,37 @@
         <v>20</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>20</v>
+        <v>226</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>20</v>
+        <v>227</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>20</v>
+        <v>228</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>338</v>
+        <v>229</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>339</v>
+        <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>130</v>
+        <v>223</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>20</v>
@@ -6598,12 +6633,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6611,13 +6646,13 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>86</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>20</v>
@@ -6626,16 +6661,16 @@
         <v>87</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>100</v>
+        <v>219</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6661,13 +6696,13 @@
         <v>20</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>195</v>
+        <v>20</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>344</v>
+        <v>20</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>345</v>
+        <v>20</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>20</v>
@@ -6685,7 +6720,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6694,7 +6729,7 @@
         <v>86</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>20</v>
+        <v>350</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>98</v>
@@ -6714,10 +6749,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6740,16 +6775,16 @@
         <v>87</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>145</v>
+        <v>100</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6775,13 +6810,13 @@
         <v>20</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>20</v>
+        <v>195</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>20</v>
+        <v>355</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>20</v>
+        <v>356</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>20</v>
@@ -6799,7 +6834,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6817,7 +6852,7 @@
         <v>20</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>352</v>
+        <v>130</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>20</v>
@@ -6828,10 +6863,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6854,16 +6889,16 @@
         <v>87</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>219</v>
+        <v>145</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6913,7 +6948,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6931,7 +6966,7 @@
         <v>20</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>130</v>
+        <v>363</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>20</v>
@@ -6942,10 +6977,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6968,16 +7003,16 @@
         <v>87</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>359</v>
+        <v>219</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7027,7 +7062,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -7042,24 +7077,24 @@
         <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>363</v>
+        <v>20</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>364</v>
+        <v>130</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>365</v>
+        <v>20</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>366</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7073,7 +7108,7 @@
         <v>86</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>20</v>
@@ -7082,16 +7117,16 @@
         <v>87</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7129,17 +7164,19 @@
         <v>20</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="AC45" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>228</v>
+        <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -7154,28 +7191,26 @@
         <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="C46" t="s" s="2">
         <v>378</v>
       </c>
+      <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>20</v>
       </c>
@@ -7202,10 +7237,10 @@
         <v>380</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7243,19 +7278,17 @@
         <v>20</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="AC46" s="2"/>
       <c r="AD46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>20</v>
+        <v>228</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -7270,26 +7303,28 @@
         <v>98</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>376</v>
+        <v>387</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="C47" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="D47" t="s" s="2">
         <v>20</v>
       </c>
@@ -7301,7 +7336,7 @@
         <v>86</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>20</v>
@@ -7310,15 +7345,17 @@
         <v>87</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="N47" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="L47" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7367,7 +7404,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -7382,7 +7419,7 @@
         <v>98</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>20</v>
+        <v>384</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>385</v>
@@ -7391,15 +7428,15 @@
         <v>386</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>20</v>
+        <v>387</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7413,7 +7450,7 @@
         <v>86</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>20</v>
@@ -7422,13 +7459,13 @@
         <v>87</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7479,7 +7516,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7497,10 +7534,10 @@
         <v>20</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>20</v>
@@ -7508,10 +7545,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7522,7 +7559,7 @@
         <v>77</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>87</v>
@@ -7534,13 +7571,13 @@
         <v>87</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7591,13 +7628,13 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
@@ -7606,24 +7643,24 @@
         <v>98</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>397</v>
+        <v>20</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>20</v>
+        <v>403</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7634,25 +7671,25 @@
         <v>77</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>219</v>
+        <v>405</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>330</v>
+        <v>406</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>331</v>
+        <v>407</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7703,25 +7740,25 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>222</v>
+        <v>404</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>20</v>
+        <v>408</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>223</v>
+        <v>409</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>20</v>
@@ -7732,21 +7769,21 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>132</v>
+        <v>20</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>20</v>
@@ -7758,17 +7795,15 @@
         <v>20</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>133</v>
+        <v>219</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>134</v>
+        <v>341</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -7817,19 +7852,19 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>138</v>
+        <v>20</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>20</v>
@@ -7846,14 +7881,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>402</v>
+        <v>132</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7866,26 +7901,24 @@
         <v>20</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>403</v>
+        <v>134</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>404</v>
+        <v>344</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="O52" t="s" s="2">
-        <v>142</v>
-      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>20</v>
       </c>
@@ -7933,7 +7966,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>405</v>
+        <v>229</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7951,7 +7984,7 @@
         <v>20</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>130</v>
+        <v>223</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>20</v>
@@ -7962,43 +7995,45 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>20</v>
+        <v>413</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="J53" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>191</v>
+        <v>133</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>415</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O53" t="s" s="2">
-        <v>409</v>
+        <v>142</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -8023,13 +8058,13 @@
         <v>20</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>195</v>
+        <v>20</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>196</v>
+        <v>20</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>410</v>
+        <v>20</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>20</v>
@@ -8047,39 +8082,39 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>411</v>
+        <v>20</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>412</v>
+        <v>130</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>413</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8087,13 +8122,13 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>86</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>20</v>
@@ -8102,17 +8137,17 @@
         <v>87</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>415</v>
+        <v>191</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
@@ -8137,13 +8172,13 @@
         <v>20</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>20</v>
+        <v>195</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>20</v>
+        <v>196</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>20</v>
+        <v>421</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>20</v>
@@ -8161,10 +8196,10 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>86</v>
@@ -8176,24 +8211,24 @@
         <v>98</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>421</v>
+        <v>20</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8201,31 +8236,33 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>86</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>219</v>
+        <v>426</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>330</v>
+        <v>427</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>331</v>
+        <v>428</v>
       </c>
       <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
+      <c r="O55" t="s" s="2">
+        <v>429</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>20</v>
       </c>
@@ -8273,10 +8310,10 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>222</v>
+        <v>425</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>86</v>
@@ -8285,38 +8322,38 @@
         <v>20</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>20</v>
+        <v>430</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>223</v>
+        <v>431</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>20</v>
+        <v>432</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>20</v>
+        <v>433</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>132</v>
+        <v>20</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>20</v>
@@ -8328,17 +8365,15 @@
         <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>133</v>
+        <v>219</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>134</v>
+        <v>341</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>20</v>
@@ -8375,31 +8410,31 @@
         <v>20</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>226</v>
+        <v>20</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>227</v>
+        <v>20</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>228</v>
+        <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>138</v>
+        <v>20</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>20</v>
@@ -8414,44 +8449,44 @@
         <v>20</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>20</v>
+        <v>132</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>219</v>
+        <v>133</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>426</v>
+        <v>134</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>337</v>
+        <v>136</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8489,37 +8524,37 @@
         <v>20</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>20</v>
+        <v>226</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>20</v>
+        <v>227</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>20</v>
+        <v>228</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>338</v>
+        <v>229</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>339</v>
+        <v>20</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>130</v>
+        <v>223</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>20</v>
@@ -8528,12 +8563,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8541,13 +8576,13 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>86</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>20</v>
@@ -8556,16 +8591,16 @@
         <v>87</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>100</v>
+        <v>219</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>341</v>
+        <v>437</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8591,13 +8626,13 @@
         <v>20</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>195</v>
+        <v>20</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>344</v>
+        <v>20</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>345</v>
+        <v>20</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>20</v>
@@ -8615,7 +8650,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8624,7 +8659,7 @@
         <v>86</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>20</v>
+        <v>350</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>98</v>
@@ -8644,10 +8679,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8670,16 +8705,16 @@
         <v>87</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>145</v>
+        <v>100</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8705,13 +8740,13 @@
         <v>20</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>20</v>
+        <v>195</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>20</v>
+        <v>355</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>20</v>
+        <v>356</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>20</v>
@@ -8729,7 +8764,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8747,7 +8782,7 @@
         <v>20</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>352</v>
+        <v>130</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>20</v>
@@ -8758,10 +8793,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8784,16 +8819,16 @@
         <v>87</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>219</v>
+        <v>145</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8843,7 +8878,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
@@ -8861,7 +8896,7 @@
         <v>20</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>130</v>
+        <v>363</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>20</v>
@@ -8870,12 +8905,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8889,27 +8924,27 @@
         <v>86</v>
       </c>
       <c r="H61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J61" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="I61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="K61" t="s" s="2">
-        <v>431</v>
+        <v>219</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>432</v>
+        <v>365</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" t="s" s="2">
-        <v>434</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>20</v>
       </c>
@@ -8957,7 +8992,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>430</v>
+        <v>368</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
@@ -8975,7 +9010,7 @@
         <v>20</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>435</v>
+        <v>130</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>20</v>
@@ -8984,12 +9019,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9003,26 +9038,26 @@
         <v>86</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>20</v>
@@ -9071,7 +9106,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
@@ -9089,21 +9124,21 @@
         <v>20</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>442</v>
+        <v>20</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9114,10 +9149,10 @@
         <v>77</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>20</v>
@@ -9126,18 +9161,18 @@
         <v>87</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>191</v>
+        <v>448</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" t="s" s="2">
+        <v>451</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>20</v>
       </c>
@@ -9161,37 +9196,37 @@
         <v>20</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>195</v>
+        <v>20</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>196</v>
+        <v>20</v>
       </c>
       <c r="Z63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF63" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="AA63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>443</v>
-      </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>20</v>
@@ -9200,24 +9235,24 @@
         <v>98</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>448</v>
+        <v>20</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9231,7 +9266,7 @@
         <v>78</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>20</v>
@@ -9240,16 +9275,16 @@
         <v>87</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>452</v>
+        <v>191</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9275,13 +9310,13 @@
         <v>20</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>20</v>
+        <v>195</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>20</v>
+        <v>196</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>20</v>
+        <v>458</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>20</v>
@@ -9299,7 +9334,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
@@ -9314,24 +9349,24 @@
         <v>98</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9345,7 +9380,7 @@
         <v>78</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>20</v>
@@ -9354,16 +9389,16 @@
         <v>87</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>191</v>
+        <v>463</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9389,13 +9424,13 @@
         <v>20</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>195</v>
+        <v>20</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>196</v>
+        <v>20</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>461</v>
+        <v>20</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>20</v>
@@ -9413,7 +9448,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
@@ -9428,24 +9463,24 @@
         <v>98</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>20</v>
+        <v>467</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>20</v>
+        <v>461</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>463</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9456,7 +9491,7 @@
         <v>77</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>87</v>
@@ -9471,13 +9506,13 @@
         <v>191</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9509,31 +9544,31 @@
         <v>196</v>
       </c>
       <c r="Z66" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF66" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="AA66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>464</v>
-      </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>20</v>
@@ -9545,21 +9580,21 @@
         <v>20</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>20</v>
+        <v>474</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9570,28 +9605,28 @@
         <v>77</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>471</v>
+        <v>191</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9617,13 +9652,13 @@
         <v>20</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>20</v>
+        <v>195</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>20</v>
+        <v>196</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>20</v>
+        <v>479</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>20</v>
@@ -9641,13 +9676,13 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>20</v>
@@ -9659,7 +9694,7 @@
         <v>20</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>20</v>
@@ -9670,10 +9705,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9696,16 +9731,16 @@
         <v>20</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>191</v>
+        <v>482</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9731,13 +9766,13 @@
         <v>20</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>195</v>
+        <v>20</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>196</v>
+        <v>20</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>480</v>
+        <v>20</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>20</v>
@@ -9755,7 +9790,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
@@ -9773,7 +9808,7 @@
         <v>20</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>20</v>
@@ -9784,10 +9819,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9810,18 +9845,18 @@
         <v>20</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>483</v>
+        <v>191</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" t="s" s="2">
-        <v>486</v>
-      </c>
+        <v>489</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>20</v>
       </c>
@@ -9845,13 +9880,13 @@
         <v>20</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>20</v>
+        <v>195</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>20</v>
+        <v>196</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>20</v>
+        <v>491</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>20</v>
@@ -9869,7 +9904,7 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
@@ -9887,7 +9922,7 @@
         <v>20</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>20</v>
@@ -9898,10 +9933,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9924,16 +9959,18 @@
         <v>20</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>191</v>
+        <v>494</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
+      <c r="O70" t="s" s="2">
+        <v>497</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>20</v>
       </c>
@@ -9957,13 +9994,13 @@
         <v>20</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>195</v>
+        <v>20</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>196</v>
+        <v>20</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>490</v>
+        <v>20</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>20</v>
@@ -9981,7 +10018,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -9999,7 +10036,7 @@
         <v>20</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>20</v>
@@ -10008,12 +10045,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10027,7 +10064,7 @@
         <v>78</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>20</v>
@@ -10036,13 +10073,13 @@
         <v>20</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>493</v>
+        <v>191</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10069,13 +10106,13 @@
         <v>20</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>20</v>
+        <v>195</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>20</v>
+        <v>196</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>20</v>
+        <v>501</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>20</v>
@@ -10093,7 +10130,7 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
@@ -10108,24 +10145,24 @@
         <v>98</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>496</v>
+        <v>20</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>498</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10139,7 +10176,7 @@
         <v>78</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>20</v>
@@ -10148,13 +10185,13 @@
         <v>20</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>394</v>
+        <v>504</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10205,7 +10242,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
@@ -10220,24 +10257,24 @@
         <v>98</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>20</v>
+        <v>507</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>20</v>
+        <v>509</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10248,7 +10285,7 @@
         <v>77</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>20</v>
@@ -10260,13 +10297,13 @@
         <v>20</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>219</v>
+        <v>405</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>330</v>
+        <v>511</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>331</v>
+        <v>512</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10317,25 +10354,25 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>222</v>
+        <v>510</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>223</v>
+        <v>513</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>20</v>
@@ -10346,21 +10383,21 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>504</v>
+        <v>514</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>504</v>
+        <v>514</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>132</v>
+        <v>20</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>20</v>
@@ -10372,17 +10409,15 @@
         <v>20</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>133</v>
+        <v>219</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>134</v>
+        <v>341</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>20</v>
@@ -10431,19 +10466,19 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>138</v>
+        <v>20</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>20</v>
@@ -10460,14 +10495,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>505</v>
+        <v>515</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>505</v>
+        <v>515</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>402</v>
+        <v>132</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10480,26 +10515,24 @@
         <v>20</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="K75" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>403</v>
+        <v>134</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>404</v>
+        <v>344</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="O75" t="s" s="2">
-        <v>142</v>
-      </c>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>20</v>
       </c>
@@ -10547,7 +10580,7 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>405</v>
+        <v>229</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>77</v>
@@ -10565,7 +10598,7 @@
         <v>20</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>130</v>
+        <v>223</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>20</v>
@@ -10576,42 +10609,46 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>506</v>
+        <v>516</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>506</v>
+        <v>516</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>20</v>
+        <v>413</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>191</v>
+        <v>133</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>507</v>
+        <v>414</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
+        <v>415</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>20</v>
       </c>
@@ -10635,13 +10672,13 @@
         <v>20</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>111</v>
+        <v>20</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>509</v>
+        <v>20</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>510</v>
+        <v>20</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>20</v>
@@ -10659,25 +10696,25 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>506</v>
+        <v>416</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>511</v>
+        <v>130</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>20</v>
@@ -10688,10 +10725,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10699,7 +10736,7 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>86</v>
@@ -10714,13 +10751,13 @@
         <v>20</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>513</v>
+        <v>191</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10747,13 +10784,13 @@
         <v>20</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>20</v>
+        <v>111</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>20</v>
+        <v>520</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>20</v>
+        <v>521</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>20</v>
@@ -10771,10 +10808,10 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AH77" t="s" s="2">
         <v>86</v>
@@ -10789,7 +10826,7 @@
         <v>20</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>20</v>
@@ -10800,10 +10837,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10811,10 +10848,10 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>20</v>
@@ -10826,20 +10863,16 @@
         <v>20</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>522</v>
-      </c>
+        <v>526</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>20</v>
       </c>
@@ -10887,13 +10920,13 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>20</v>
@@ -10905,7 +10938,7 @@
         <v>20</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>20</v>
@@ -10916,10 +10949,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10942,18 +10975,20 @@
         <v>20</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>191</v>
+        <v>529</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="O79" s="2"/>
+        <v>532</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>533</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>20</v>
       </c>
@@ -10977,13 +11012,13 @@
         <v>20</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>195</v>
+        <v>20</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>196</v>
+        <v>20</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>527</v>
+        <v>20</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>20</v>
@@ -11001,7 +11036,7 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>77</v>
@@ -11019,17 +11054,131 @@
         <v>20</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN79" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN80" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN79">
+  <autoFilter ref="A1:AN80">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11039,7 +11188,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI78">
+  <conditionalFormatting sqref="A2:AI79">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LTCProcedureCareActivity.xlsx
+++ b/docs/StructureDefinition-LTCProcedureCareActivity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03T21:17:06+08:00</t>
+    <t>2026-06-25T08:48:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
